--- a/etf_holdings/2026-08-24_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:44</t>
+          <t>2026-08-24 16:04:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:46</t>
+          <t>2026-08-24 16:04:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:47</t>
+          <t>2026-08-24 16:05:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:48</t>
+          <t>2026-08-24 16:05:02</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-24_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:58</t>
+          <t>2026-08-24 16:24:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:59</t>
+          <t>2026-08-24 16:24:08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:00</t>
+          <t>2026-08-24 16:24:09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:02</t>
+          <t>2026-08-24 16:24:11</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-24_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:07</t>
+          <t>2026-08-24 16:42:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:08</t>
+          <t>2026-08-24 16:42:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:09</t>
+          <t>2026-08-24 16:42:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-24 16:24:11</t>
+          <t>2026-08-24 16:42:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-24_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:26</t>
+          <t>2026-08-24 16:55:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:27</t>
+          <t>2026-08-24 16:55:57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:28</t>
+          <t>2026-08-24 16:55:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:30</t>
+          <t>2026-08-24 16:56:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-24_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.87%1,794,000</t>
+          <t>8.74%1,794,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.87%</t>
+          <t>8.74%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.78%872,000</t>
+          <t>6.73%872,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.78%</t>
+          <t>6.73%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.54%510,000</t>
+          <t>6.59%510,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.54%</t>
+          <t>6.59%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.98%3,828,000</t>
+          <t>5.95%3,828,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.98%</t>
+          <t>5.95%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.08%185,000</t>
+          <t>5.47%185,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.08%</t>
+          <t>5.47%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-4.4%5430</t>
+          <t>-1.43%2070</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5430</v>
+        <v>2070</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.73%320,000</t>
+          <t>3.58%844,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>320000</v>
+        <v>844000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3105穩懋</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.83%355</t>
+          <t>-4.4%5430</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.83%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>355</v>
+        <v>5430</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.68%4,809,000</t>
+          <t>3.56%320,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4809000</v>
+        <v>320000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.43%2070</t>
+          <t>+1.83%5565</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2070</v>
+        <v>5565</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.63%844,000</t>
+          <t>3.50%307,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>844000</v>
+        <v>307000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3105穩懋</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.83%5565</t>
+          <t>-4.83%355</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>-4.83%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5565</v>
+        <v>355</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.44%307,000</t>
+          <t>3.50%4,809,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>307000</v>
+        <v>4809000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,20 +1071,20 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.41%817,000</t>
+          <t>3.09%727,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>817000</v>
+        <v>727000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.99%1,650,000</t>
+          <t>2.86%1,650,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.01%5385</t>
+          <t>-1.25%435.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5385</v>
+        <v>435.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.96%257,000</t>
+          <t>2.84%3,178,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>257000</v>
+        <v>3178000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.25%435.5</t>
+          <t>-4.01%5385</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-4.01%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>435.5</v>
+        <v>5385</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.87%3,178,000</t>
+          <t>2.84%257,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>3178000</v>
+        <v>257000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.62%1,000,000</t>
+          <t>2.65%1,000,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.65%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:56</t>
+          <t>2026-08-24 19:59:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.35%2855</t>
+          <t>+7.33%1010</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+7.33%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2855</v>
+        <v>1010</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.23%379,000</t>
+          <t>2.31%1,117,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>379000</v>
+        <v>1117000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+7.33%1010</t>
+          <t>-0.35%2855</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+7.33%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1010</v>
+        <v>2855</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.16%1,117,000</t>
+          <t>2.22%379,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1117000</v>
+        <v>379000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.67%1,158,000</t>
+          <t>1.63%1,158,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,16 +1559,16 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.66%3,985,000</t>
+          <t>1.37%3,242,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3985000</v>
+        <v>3242000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.68%1455</t>
+          <t>+9.96%287</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>+9.96%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1455</v>
+        <v>287</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.33%434,000</t>
+          <t>1.35%2,289,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>434000</v>
+        <v>2289000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.03%381.5</t>
+          <t>+6.01%123.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.03%</t>
+          <t>+6.01%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>381.5</v>
+        <v>123.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.31%1,572,000</t>
+          <t>1.34%5,285,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1572000</v>
+        <v>5285000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6214精誠</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0%179.5</t>
+          <t>+3.13%181.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+3.13%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>179.5</v>
+        <v>181.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.29%3,504,000</t>
+          <t>1.32%3,533,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>3504000</v>
+        <v>3533000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+3.13%181.5</t>
+          <t>+1.77%144</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>+1.77%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>181.5</v>
+        <v>144</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.27%3,533,000</t>
+          <t>1.30%4,386,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3533000</v>
+        <v>4386000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.77%144</t>
+          <t>-2.68%1455</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>144</v>
+        <v>1455</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.27%4,386,000</t>
+          <t>1.30%434,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>4386000</v>
+        <v>434000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6214精誠</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+6.01%123.5</t>
+          <t>0%179.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+6.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>123.5</v>
+        <v>179.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.26%5,285,000</t>
+          <t>1.29%3,504,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>5285000</v>
+        <v>3504000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.25%1,800,000</t>
+          <t>1.26%1,800,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,25 +2090,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+9.96%287</t>
+          <t>-6.03%381.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-6.03%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>287</v>
+        <v>381.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.23%2,289,000</t>
+          <t>1.23%1,572,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>2289000</v>
+        <v>1572000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2428興勤</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.18%250.5</t>
+          <t>+1.39%658</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+1.39%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>250.5</v>
+        <v>658</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.22%2,356,000</t>
+          <t>1.22%901,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>2356000</v>
+        <v>901000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>2428興勤</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+1.39%658</t>
+          <t>-1.18%250.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>658</v>
+        <v>250.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.20%901,000</t>
+          <t>1.21%2,356,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>901000</v>
+        <v>2356000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:57</t>
+          <t>2026-08-24 19:59:11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.19%3,472,000</t>
+          <t>1.18%3,472,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.15%959,000</t>
+          <t>1.16%959,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.15%3,396,000</t>
+          <t>1.14%3,396,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-4.82%533</t>
+          <t>-1.53%15115</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-4.82%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>533</v>
+        <v>15115</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.15%1,000,000</t>
+          <t>1.11%35,900</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1000000</v>
+        <v>35900</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.14%4,484,000</t>
+          <t>1.11%4,484,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.53%15115</t>
+          <t>-4.82%533</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>-4.82%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>15115</v>
+        <v>533</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.13%35,900</t>
+          <t>1.09%1,000,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>35900</v>
+        <v>1000000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+5.05%1145</t>
+          <t>+0.75%269.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>+0.75%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1145</v>
+        <v>269.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.85%382,000</t>
+          <t>1.06%1,910,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>382000</v>
+        <v>1910000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5536聖暉*</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.27%860</t>
+          <t>+5.05%1145</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>+5.05%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>860</v>
+        <v>1145</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.83%459,000</t>
+          <t>0.90%382,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>459000</v>
+        <v>382000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6472保瑞</t>
+          <t>5536聖暉*</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.44%453</t>
+          <t>-2.27%860</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-2.27%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>453</v>
+        <v>860</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.48%516,000</t>
+          <t>0.81%459,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>516000</v>
+        <v>459000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2486一詮</t>
+          <t>6472保瑞</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.26%249</t>
+          <t>-0.44%453</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>249</v>
+        <v>453</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.47%950,000</t>
+          <t>0.72%774,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>950000</v>
+        <v>774000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,34 +2883,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>2486一詮</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+2.09%2200</t>
+          <t>+2.26%249</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+2.09%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2200</v>
+        <v>249</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.41%93,000</t>
+          <t>0.49%950,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>93000</v>
+        <v>950000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.75%269.5</t>
+          <t>+2.09%2200</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>+2.09%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>269.5</v>
+        <v>2200</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.39%710,000</t>
+          <t>0.42%93,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>710000</v>
+        <v>93000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>3617碩天</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-5.95%482.5</t>
+          <t>-0.77%257.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-5.95%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>482.5</v>
+        <v>257.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.34%321,000</t>
+          <t>0.32%603,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>321000</v>
+        <v>603000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3617碩天</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.77%257.5</t>
+          <t>-5.95%482.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-5.95%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>257.5</v>
+        <v>482.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.32%603,000</t>
+          <t>0.32%321,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>603000</v>
+        <v>321000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:59</t>
+          <t>2026-08-24 19:59:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.30%546,000</t>
+          <t>0.29%546,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,25 +3310,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>8070長華*</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.5%62.4</t>
+          <t>+0.41%49</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>62.4</v>
+        <v>49</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.29%2,213,556</t>
+          <t>0.29%2,871,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>2213556</v>
+        <v>2871000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8070長華*</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.41%49</t>
+          <t>-2.5%62.4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>49</v>
+        <v>62.4</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.29%2,871,000</t>
+          <t>0.28%2,213,556</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>2871000</v>
+        <v>2213556</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.28%1,544,000</t>
+          <t>0.27%1,544,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.12%42,000</t>
+          <t>0.13%42,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:00</t>
+          <t>2026-08-24 19:59:14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-24_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:10</t>
+          <t>2026-08-24 23:03:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:11</t>
+          <t>2026-08-24 23:03:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:12</t>
+          <t>2026-08-24 23:03:51</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:14</t>
+          <t>2026-08-24 23:03:52</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
